--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6271-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6271-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D62E8143-DC2C-4F04-8E11-E1F0463317EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D156B319-BB3F-406E-9F9A-170C22182D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{23F7806A-AFEA-452F-B303-D051FC884FCC}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{200107BF-7BF8-4C87-90E7-35CAE05B7019}"/>
   </bookViews>
   <sheets>
     <sheet name="6271-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1571,28 +1571,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E02EACF-FE99-488F-8A3D-72F6B7738DB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94291C13-0338-428C-9B7F-8AC10D7CE55D}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1626,7 @@
       <c r="W1" s="33"/>
       <c r="X1" s="25"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1662,7 +1662,7 @@
       <c r="W2" s="35"/>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="X3" s="39"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1782,7 +1782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>2025</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>2024</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2023</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="44">
         <v>2022</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="46"/>
       <c r="B16" s="47"/>
       <c r="C16" s="20" t="s">
@@ -2616,7 +2616,7 @@
       <c r="W16" s="53"/>
       <c r="X16" s="49"/>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="50" t="s">
         <v>29</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="51"/>
       <c r="B18" s="51"/>
       <c r="C18" s="22" t="s">
@@ -2718,7 +2718,7 @@
       <c r="W18" s="53"/>
       <c r="X18" s="49"/>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <v>2021</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="42">
         <v>2020</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>2019</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="42">
         <v>2018</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>2017</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="42">
         <v>2016</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <v>2015</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="42">
         <v>2014</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>2013</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="42">
         <v>2012</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2011</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="42">
         <v>2010</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2009</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="42">
         <v>2008</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
         <v>2007</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="42">
         <v>2006</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>2005</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="42">
         <v>2004</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>2003</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="42">
         <v>2002</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>2001</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="42">
         <v>2000</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>1999</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="42" t="s">
         <v>61</v>
       </c>
